--- a/OnlineBookmark/bookmarks/projects/project workflow.xlsx
+++ b/OnlineBookmark/bookmarks/projects/project workflow.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Main/Sub</t>
   </si>
@@ -163,6 +163,10 @@
   </si>
   <si>
     <t xml:space="preserve">1. user 屬於 BKM_ADM group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open / 
+Outer Approve</t>
   </si>
   <si>
     <t xml:space="preserve">1. 輸入 main task 必填內容:
@@ -176,14 +180,20 @@
   </si>
   <si>
     <t xml:space="preserve">1. 建立 main task
-2. main task assignee --&gt; SignoffPerson 欄位中第一人
+2. 如果 OuterSignOffperson 有內容:
+  - main task status 推到 Outer Apprive
+  - main task assignee --&gt; OuterSignOffperson 欄位中第一人
+3. 如果 OuterSugnOffperson 沒有內容:
+  - main task status 推到 Open
+  - main task assignee --&gt; SignoffPerson 欄位中第一人
 3. send email to assignee</t>
   </si>
   <si>
     <t xml:space="preserve">1. user = assignee</t>
   </si>
   <si>
-    <t xml:space="preserve">Open / Effective</t>
+    <t xml:space="preserve">Open / 
+Effective</t>
   </si>
   <si>
     <t xml:space="preserve">1. 如果 SignoffPerson 還有要簽的人:
@@ -196,6 +206,22 @@
 3. send email to assignee</t>
   </si>
   <si>
+    <t xml:space="preserve">Outer Approve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outer Approve / 
+Approve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 如果 OuterSignOffperson 還有要簽的人:
+  - status 停在 Outer Approve
+  - assignee --&gt; OuterSignOffperson 欄位中下一人
+2. 如果 OuterSignOffperson 裡面的人已經合部簽完:
+  - status 推到 Open
+  - assignee --&gt; SignoffPerson 欄位中第一人
+3. send email to assignee</t>
+  </si>
+  <si>
     <t xml:space="preserve">1. 系統在 Main Task 自動建立</t>
   </si>
   <si>
@@ -204,6 +230,11 @@
   </si>
   <si>
     <t>Complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">修改 sub task 簽核單內容
+1. 輸入必要內容
+2. 上傳 attachment</t>
   </si>
   <si>
     <t xml:space="preserve">1. assignee --&gt; creator
@@ -811,7 +842,7 @@
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -834,7 +865,7 @@
       <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -857,7 +888,7 @@
       <c r="F4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -899,7 +930,7 @@
         <v>27</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>28</v>
       </c>
     </row>
@@ -940,7 +971,7 @@
       <c r="F8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1024,7 +1055,7 @@
       <c r="F14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1044,7 +1075,7 @@
       <c r="E15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1064,7 +1095,7 @@
       <c r="E16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1084,7 +1115,7 @@
       <c r="E17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="3" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1104,9 +1135,9 @@
     <col bestFit="1" customWidth="1" min="2" max="2" width="19.00390625"/>
     <col bestFit="1" customWidth="1" min="3" max="3" width="16.140625"/>
     <col bestFit="1" customWidth="1" min="4" max="4" width="32.57421875"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="19.00390625"/>
+    <col customWidth="1" min="5" max="5" width="21.7109375"/>
     <col customWidth="1" min="6" max="6" width="56.140625"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="46.8515625"/>
+    <col customWidth="1" min="7" max="7" width="54.7109375"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,14 +1174,14 @@
       <c r="D2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
+      <c r="E2" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" ht="114">
@@ -1164,24 +1195,36 @@
         <v>26</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="1" t="s">
         <v>45</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" ht="99.75">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="G4" s="4" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
@@ -1233,14 +1276,14 @@
         <v>36</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="4" t="s">
-        <v>48</v>
+      <c r="G8" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="9" ht="42.75">
@@ -1254,14 +1297,16 @@
         <v>26</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
